--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116630733</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116630733</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116630733</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116630733</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4457,6 +4457,555 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132059783</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96483</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>210</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långhundra, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>656120</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6630866</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 st sporkapslar</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Adina Sennblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132045715</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101251</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långhundra, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>655991</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6630913</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132045712</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101251</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långhundra, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>655973</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6630966</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132059782</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96483</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>210</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långhundra, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>656140</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6630854</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Adina Sennblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132045713</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101251</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långhundra, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>655976</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6630950</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -4583,7 +4583,7 @@
         <v>132045715</v>
       </c>
       <c r="B32" t="n">
-        <v>101251</v>
+        <v>101252</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132045712</v>
       </c>
       <c r="B33" t="n">
-        <v>101251</v>
+        <v>101252</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>132045713</v>
       </c>
       <c r="B35" t="n">
-        <v>101251</v>
+        <v>101252</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -4462,7 +4462,7 @@
         <v>132059783</v>
       </c>
       <c r="B31" t="n">
-        <v>96483</v>
+        <v>96488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>132045715</v>
       </c>
       <c r="B32" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132045712</v>
       </c>
       <c r="B33" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>132059782</v>
       </c>
       <c r="B34" t="n">
-        <v>96483</v>
+        <v>96488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>132045713</v>
       </c>
       <c r="B35" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -4462,7 +4462,7 @@
         <v>132059783</v>
       </c>
       <c r="B31" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>132045715</v>
       </c>
       <c r="B32" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132045712</v>
       </c>
       <c r="B33" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>132059782</v>
       </c>
       <c r="B34" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>132045713</v>
       </c>
       <c r="B35" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5006,6 +5006,969 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132474637</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>656145</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6631085</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132474638</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>656131</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6631081</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132474636</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91855</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>656183</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6631070</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132474644</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>656014</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6630888</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132474645</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>656015</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6630892</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132474642</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>655988</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6630935</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132474630</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>656373</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6631018</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132474640</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>655985</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6630941</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132474634</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>656241</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6630936</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -5008,32 +5008,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132474637</v>
+        <v>132474638</v>
       </c>
       <c r="B36" t="n">
-        <v>101304</v>
+        <v>57945</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>656145</v>
+        <v>656131</v>
       </c>
       <c r="R36" t="n">
-        <v>6631085</v>
+        <v>6631081</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5115,32 +5115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132474638</v>
+        <v>132474637</v>
       </c>
       <c r="B37" t="n">
-        <v>57945</v>
+        <v>101304</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>656131</v>
+        <v>656145</v>
       </c>
       <c r="R37" t="n">
-        <v>6631081</v>
+        <v>6631085</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -4462,7 +4462,7 @@
         <v>132059783</v>
       </c>
       <c r="B31" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>132045715</v>
       </c>
       <c r="B32" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132045712</v>
       </c>
       <c r="B33" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>132059782</v>
       </c>
       <c r="B34" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>132045713</v>
       </c>
       <c r="B35" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>132474638</v>
       </c>
       <c r="B36" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>132474637</v>
       </c>
       <c r="B37" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>132474636</v>
       </c>
       <c r="B38" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>132474644</v>
       </c>
       <c r="B39" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>132474645</v>
       </c>
       <c r="B40" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132474642</v>
+        <v>132474630</v>
       </c>
       <c r="B41" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655988</v>
+        <v>656373</v>
       </c>
       <c r="R41" t="n">
-        <v>6630935</v>
+        <v>6631018</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5650,10 +5650,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132474630</v>
+        <v>132474642</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>101312</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5661,21 +5661,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656373</v>
+        <v>655988</v>
       </c>
       <c r="R42" t="n">
-        <v>6631018</v>
+        <v>6630935</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5760,7 +5760,7 @@
         <v>132474640</v>
       </c>
       <c r="B43" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -4462,7 +4462,7 @@
         <v>132059783</v>
       </c>
       <c r="B31" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>132045715</v>
       </c>
       <c r="B32" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132045712</v>
       </c>
       <c r="B33" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>132059782</v>
       </c>
       <c r="B34" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>132045713</v>
       </c>
       <c r="B35" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>132474638</v>
       </c>
       <c r="B36" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>132474637</v>
       </c>
       <c r="B37" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>132474636</v>
       </c>
       <c r="B38" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>132474644</v>
       </c>
       <c r="B39" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>132474645</v>
       </c>
       <c r="B40" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132474630</v>
+        <v>132474642</v>
       </c>
       <c r="B41" t="n">
-        <v>4781</v>
+        <v>101323</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656373</v>
+        <v>655988</v>
       </c>
       <c r="R41" t="n">
-        <v>6631018</v>
+        <v>6630935</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5650,10 +5650,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132474642</v>
+        <v>132474630</v>
       </c>
       <c r="B42" t="n">
-        <v>101312</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5661,21 +5661,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655988</v>
+        <v>656373</v>
       </c>
       <c r="R42" t="n">
-        <v>6630935</v>
+        <v>6631018</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5760,7 +5760,7 @@
         <v>132474640</v>
       </c>
       <c r="B43" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -5118,7 +5118,7 @@
         <v>132474637</v>
       </c>
       <c r="B37" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>132474636</v>
       </c>
       <c r="B38" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>132474644</v>
       </c>
       <c r="B39" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>132474645</v>
       </c>
       <c r="B40" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>132474642</v>
       </c>
       <c r="B41" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>132474640</v>
       </c>
       <c r="B43" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116630733</v>
+        <v>132059781</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Långhundra, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656371</v>
+        <v>656106</v>
       </c>
       <c r="R2" t="n">
-        <v>6630965</v>
+        <v>6630856</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 kapslar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,34 +778,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Berg</t>
+          <t>Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Berg</t>
+          <t>Eduardo Ottimofiore, Adina Sennblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119077569</v>
+        <v>132059782</v>
       </c>
       <c r="B3" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,51 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Långhundra, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656051</v>
+        <v>656140</v>
       </c>
       <c r="R3" t="n">
-        <v>6631000</v>
+        <v>6630854</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,79 +891,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Eduardo Ottimofiore, Adina Sennblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119077949</v>
+        <v>132059783</v>
       </c>
       <c r="B4" t="n">
-        <v>57224</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Långhundra, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656274</v>
+        <v>656120</v>
       </c>
       <c r="R4" t="n">
-        <v>6630972</v>
+        <v>6630866</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,27 +977,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>2 st sporkapslar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,27 +1012,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Eduardo Ottimofiore, Adina Sennblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119077576</v>
+        <v>132474631</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,51 +1035,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656185</v>
+        <v>656384</v>
       </c>
       <c r="R5" t="n">
-        <v>6630856</v>
+        <v>6630887</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,27 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,79 +1119,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119077585</v>
+        <v>132474645</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656312</v>
+        <v>656015</v>
       </c>
       <c r="R6" t="n">
-        <v>6630841</v>
+        <v>6630892</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:59</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,27 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119077950</v>
+        <v>132474625</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,51 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656268</v>
+        <v>656381</v>
       </c>
       <c r="R7" t="n">
-        <v>6630973</v>
+        <v>6631065</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,27 +1303,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,27 +1333,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119076752</v>
+        <v>132474641</v>
       </c>
       <c r="B8" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,51 +1356,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656299</v>
+        <v>655985</v>
       </c>
       <c r="R8" t="n">
-        <v>6631039</v>
+        <v>6630941</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1530,27 +1410,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:09</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,79 +1440,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119077580</v>
+        <v>132474636</v>
       </c>
       <c r="B9" t="n">
-        <v>57555</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656196</v>
+        <v>656183</v>
       </c>
       <c r="R9" t="n">
-        <v>6630864</v>
+        <v>6631070</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1661,27 +1517,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1696,27 +1547,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119076750</v>
+        <v>132474615</v>
       </c>
       <c r="B10" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,16 +1570,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1741,34 +1587,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656263</v>
+        <v>656402</v>
       </c>
       <c r="R10" t="n">
-        <v>6631016</v>
+        <v>6631028</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1792,27 +1624,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,27 +1659,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119076736</v>
+        <v>132474638</v>
       </c>
       <c r="B11" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,16 +1682,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1872,34 +1699,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656143</v>
+        <v>656131</v>
       </c>
       <c r="R11" t="n">
-        <v>6630950</v>
+        <v>6631081</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1923,27 +1736,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>05:33</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>05:33</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1958,27 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119077952</v>
+        <v>119077949</v>
       </c>
       <c r="B12" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,16 +1789,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>100067</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2010,7 +1813,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2024,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656270</v>
+        <v>656274</v>
       </c>
       <c r="R12" t="n">
-        <v>6631017</v>
+        <v>6630972</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2059,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2069,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2101,15 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119077613</v>
+        <v>132474630</v>
       </c>
       <c r="B13" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,51 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sydöstra stadsdelarna, Upl</t>
+          <t>Halmby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656173</v>
+        <v>656373</v>
       </c>
       <c r="R13" t="n">
-        <v>6631129</v>
+        <v>6631018</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2185,27 +1969,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>05:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>05:39</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Uppsala kommun.</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2220,44 +1999,39 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Erik Berg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119077572</v>
+        <v>119077579</v>
       </c>
       <c r="B14" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2286,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656140</v>
+        <v>656191</v>
       </c>
       <c r="R14" t="n">
-        <v>6630889</v>
+        <v>6630854</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2321,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2331,7 +2105,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2363,32 +2137,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119077963</v>
+        <v>119077936</v>
       </c>
       <c r="B15" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2417,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656029</v>
+        <v>656162</v>
       </c>
       <c r="R15" t="n">
-        <v>6631181</v>
+        <v>6630848</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2452,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2462,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2494,37 +2263,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119077967</v>
+        <v>119077611</v>
       </c>
       <c r="B16" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2534,7 +2298,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2548,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655921</v>
+        <v>656242</v>
       </c>
       <c r="R16" t="n">
-        <v>6631127</v>
+        <v>6631094</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2578,22 +2342,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2625,37 +2389,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119077622</v>
+        <v>119077580</v>
       </c>
       <c r="B17" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2665,7 +2424,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2679,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656005</v>
+        <v>656196</v>
       </c>
       <c r="R17" t="n">
-        <v>6631189</v>
+        <v>6630864</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2714,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2724,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2756,15 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119077944</v>
+        <v>119076730</v>
       </c>
       <c r="B18" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,16 +2526,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2796,7 +2550,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2810,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656275</v>
+        <v>655990</v>
       </c>
       <c r="R18" t="n">
-        <v>6630795</v>
+        <v>6630947</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2840,22 +2594,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2887,15 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119077623</v>
+        <v>119076736</v>
       </c>
       <c r="B19" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,16 +2652,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2922,7 +2671,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2941,10 +2690,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656004</v>
+        <v>656143</v>
       </c>
       <c r="R19" t="n">
-        <v>6631169</v>
+        <v>6630950</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2971,22 +2720,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:28</t>
+          <t>05:33</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3018,15 +2767,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119077954</v>
+        <v>119076740</v>
       </c>
       <c r="B20" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3072,10 +2816,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656355</v>
+        <v>656193</v>
       </c>
       <c r="R20" t="n">
-        <v>6631092</v>
+        <v>6630858</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -3102,22 +2846,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3149,37 +2893,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119077611</v>
+        <v>119076750</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3203,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656242</v>
+        <v>656263</v>
       </c>
       <c r="R21" t="n">
-        <v>6631094</v>
+        <v>6631016</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -3233,22 +2972,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3280,15 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119076730</v>
+        <v>119076752</v>
       </c>
       <c r="B22" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3334,10 +3068,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655990</v>
+        <v>656299</v>
       </c>
       <c r="R22" t="n">
-        <v>6630947</v>
+        <v>6631039</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3369,7 +3103,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3379,7 +3113,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:09</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3411,15 +3145,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119077943</v>
+        <v>119077569</v>
       </c>
       <c r="B23" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3427,16 +3156,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3451,7 +3180,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3465,10 +3194,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656264</v>
+        <v>656051</v>
       </c>
       <c r="R23" t="n">
-        <v>6630771</v>
+        <v>6631000</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3495,22 +3224,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3542,15 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119077969</v>
+        <v>119077572</v>
       </c>
       <c r="B24" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3558,16 +3282,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3582,7 +3306,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3596,10 +3320,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655897</v>
+        <v>656140</v>
       </c>
       <c r="R24" t="n">
-        <v>6631192</v>
+        <v>6630889</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3626,22 +3350,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3673,15 +3397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119077936</v>
+        <v>119077601</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3689,16 +3408,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3713,7 +3432,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3727,10 +3446,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656162</v>
+        <v>656347</v>
       </c>
       <c r="R25" t="n">
-        <v>6630848</v>
+        <v>6630930</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3757,22 +3476,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3804,32 +3523,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119077962</v>
+        <v>119077613</v>
       </c>
       <c r="B26" t="n">
-        <v>57951</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3844,7 +3558,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3858,10 +3572,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>656097</v>
+        <v>656173</v>
       </c>
       <c r="R26" t="n">
-        <v>6631127</v>
+        <v>6631129</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3888,22 +3602,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:39</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3935,15 +3649,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119076740</v>
+        <v>119077954</v>
       </c>
       <c r="B27" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3989,10 +3698,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656193</v>
+        <v>656355</v>
       </c>
       <c r="R27" t="n">
-        <v>6630858</v>
+        <v>6631092</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -4019,22 +3728,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4066,15 +3775,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119077606</v>
+        <v>119077963</v>
       </c>
       <c r="B28" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4082,16 +3786,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4101,12 +3805,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4120,10 +3824,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656293</v>
+        <v>656029</v>
       </c>
       <c r="R28" t="n">
-        <v>6631011</v>
+        <v>6631181</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -4150,22 +3854,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4197,15 +3901,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119077579</v>
+        <v>119077967</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4213,16 +3912,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4237,7 +3936,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4251,10 +3950,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656191</v>
+        <v>655921</v>
       </c>
       <c r="R29" t="n">
-        <v>6630854</v>
+        <v>6631127</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -4281,22 +3980,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4328,32 +4027,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119077601</v>
+        <v>119077962</v>
       </c>
       <c r="B30" t="n">
-        <v>57677</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4368,7 +4062,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4382,10 +4076,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656347</v>
+        <v>656097</v>
       </c>
       <c r="R30" t="n">
-        <v>6630930</v>
+        <v>6631127</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -4412,22 +4106,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4459,10 +4153,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132059783</v>
+        <v>119077585</v>
       </c>
       <c r="B31" t="n">
-        <v>96555</v>
+        <v>58636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4470,46 +4164,51 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>210</v>
+        <v>103044</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långhundra, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656120</v>
+        <v>656312</v>
       </c>
       <c r="R31" t="n">
-        <v>6630866</v>
+        <v>6630841</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4533,27 +4232,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2 st sporkapslar</t>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4568,22 +4267,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Adina Sennblad</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132045715</v>
+        <v>119077606</v>
       </c>
       <c r="B32" t="n">
-        <v>101327</v>
+        <v>58636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,37 +4290,51 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långhundra, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655991</v>
+        <v>656293</v>
       </c>
       <c r="R32" t="n">
-        <v>6630913</v>
+        <v>6631011</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4645,22 +4358,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4675,22 +4393,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132045712</v>
+        <v>119077622</v>
       </c>
       <c r="B33" t="n">
-        <v>101327</v>
+        <v>58636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4698,37 +4416,51 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långhundra, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655973</v>
+        <v>656005</v>
       </c>
       <c r="R33" t="n">
-        <v>6630966</v>
+        <v>6631189</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4752,22 +4484,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>05:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4782,22 +4519,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132059782</v>
+        <v>119077623</v>
       </c>
       <c r="B34" t="n">
-        <v>96555</v>
+        <v>58636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4805,37 +4542,51 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>210</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långhundra, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>656140</v>
+        <v>656004</v>
       </c>
       <c r="R34" t="n">
-        <v>6630854</v>
+        <v>6631169</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4859,22 +4610,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>05:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4889,22 +4645,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Adina Sennblad</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132045713</v>
+        <v>119077943</v>
       </c>
       <c r="B35" t="n">
-        <v>101327</v>
+        <v>58636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4912,37 +4668,51 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långhundra, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655976</v>
+        <v>656264</v>
       </c>
       <c r="R35" t="n">
-        <v>6630950</v>
+        <v>6630771</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4966,22 +4736,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4996,39 +4771,39 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132474638</v>
+        <v>119077944</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>58636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5036,20 +4811,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>656131</v>
+        <v>656275</v>
       </c>
       <c r="R36" t="n">
-        <v>6631081</v>
+        <v>6630795</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5073,22 +4862,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5103,22 +4897,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132474637</v>
+        <v>119077950</v>
       </c>
       <c r="B37" t="n">
-        <v>101338</v>
+        <v>58636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5126,37 +4920,51 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>656145</v>
+        <v>656268</v>
       </c>
       <c r="R37" t="n">
-        <v>6631085</v>
+        <v>6630973</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5180,22 +4988,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5210,22 +5023,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132474636</v>
+        <v>119077952</v>
       </c>
       <c r="B38" t="n">
-        <v>91881</v>
+        <v>58636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5233,37 +5046,51 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>103044</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>656183</v>
+        <v>656270</v>
       </c>
       <c r="R38" t="n">
-        <v>6631070</v>
+        <v>6631017</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5287,22 +5114,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5317,22 +5149,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132474644</v>
+        <v>119077969</v>
       </c>
       <c r="B39" t="n">
-        <v>101338</v>
+        <v>58636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5340,37 +5172,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>656014</v>
+        <v>655897</v>
       </c>
       <c r="R39" t="n">
-        <v>6630888</v>
+        <v>6631192</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5394,22 +5240,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5424,22 +5275,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132474645</v>
+        <v>119077576</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>58676</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5447,37 +5298,51 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>103055</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>656015</v>
+        <v>656185</v>
       </c>
       <c r="R40" t="n">
-        <v>6630892</v>
+        <v>6630856</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5501,22 +5366,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5531,22 +5401,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132474630</v>
+        <v>132474634</v>
       </c>
       <c r="B41" t="n">
-        <v>4781</v>
+        <v>8460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5554,21 +5424,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5578,13 +5448,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656373</v>
+        <v>656241</v>
       </c>
       <c r="R41" t="n">
-        <v>6631018</v>
+        <v>6630936</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5613,7 +5483,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5623,7 +5493,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5650,10 +5520,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132474642</v>
+        <v>119077960</v>
       </c>
       <c r="B42" t="n">
-        <v>101338</v>
+        <v>58085</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5661,37 +5531,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>205976</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Sydöstra stadsdelarna, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655988</v>
+        <v>656238</v>
       </c>
       <c r="R42" t="n">
-        <v>6630935</v>
+        <v>6631151</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5715,22 +5599,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Uppsala kommun.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5745,22 +5634,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Väg och Miljö AB, Erik Berg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132474640</v>
+        <v>132045712</v>
       </c>
       <c r="B43" t="n">
-        <v>101338</v>
+        <v>101403</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5788,14 +5677,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Långhundra, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655985</v>
+        <v>655973</v>
       </c>
       <c r="R43" t="n">
-        <v>6630941</v>
+        <v>6630966</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5822,22 +5711,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5852,22 +5741,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Eduardo Ottimofiore, Elliot Örjes</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132474634</v>
+        <v>132045713</v>
       </c>
       <c r="B44" t="n">
-        <v>8455</v>
+        <v>101403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5875,34 +5764,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Halmby, Upl</t>
+          <t>Långhundra, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656241</v>
+        <v>655976</v>
       </c>
       <c r="R44" t="n">
-        <v>6630936</v>
+        <v>6630950</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5929,22 +5818,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5959,15 +5848,871 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132045715</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långhundra, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>655991</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6630913</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132474614</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>656401</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6631017</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132474623</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>656386</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6631065</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132474629</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>656381</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6631009</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132474637</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>656145</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6631085</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132474640</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>655985</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6630941</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132474642</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>655988</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6630935</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132474644</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Halmby, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>656014</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6630888</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49894-2023 artfynd.xlsx
+++ b/artfynd/A 49894-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059782</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474631</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474645</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474625</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474641</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474636</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474615</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1775,6 +1825,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474638</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1901,6 +1956,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077949</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474630</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2134,6 +2199,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077579</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,6 +2330,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077936</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2386,6 +2461,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077611</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2512,6 +2592,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077580</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2638,6 +2723,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119076730</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2764,6 +2854,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119076736</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2890,6 +2985,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119076740</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3016,6 +3116,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119076750</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3142,6 +3247,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119076752</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3268,6 +3378,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077569</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3394,6 +3509,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077572</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3520,6 +3640,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077601</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3646,6 +3771,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077613</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3772,6 +3902,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077954</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3898,6 +4033,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077963</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4024,6 +4164,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077967</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4150,6 +4295,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077962</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4276,6 +4426,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077585</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4402,6 +4557,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077606</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4528,6 +4688,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077622</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4654,6 +4819,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077623</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4780,6 +4950,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077943</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4906,6 +5081,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077944</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5032,6 +5212,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077950</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5158,6 +5343,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077952</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5284,6 +5474,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077969</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5410,6 +5605,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077576</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5517,6 +5717,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474634</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5643,6 +5848,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119077960</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5750,6 +5960,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132045712</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5857,6 +6072,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132045713</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5964,6 +6184,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132045715</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6071,6 +6296,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474614</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6178,6 +6408,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474623</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6285,6 +6520,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474629</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6392,6 +6632,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474637</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6499,6 +6744,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474640</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6606,6 +6856,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474642</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6713,8 +6968,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132474644</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>